--- a/main/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T08:08:15+00:00</t>
+    <t>2026-05-18T14:11:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T14:11:29+00:00</t>
+    <t>2026-05-21T09:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T09:18:21+00:00</t>
+    <t>2026-06-01T14:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:41:15+00:00</t>
+    <t>2026-06-01T15:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T15:18:33+00:00</t>
+    <t>2026-06-02T07:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$89</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3694" uniqueCount="657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3424" uniqueCount="612">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T07:35:19+00:00</t>
+    <t>2026-06-04T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1498,40 +1498,37 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/extension-bodysite.html).</t>
   </si>
   <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+  </si>
+  <si>
+    <t>&lt; 123037004 |Body structure|</t>
+  </si>
+  <si>
+    <t>OBX-20</t>
+  </si>
+  <si>
+    <t>targetSiteCode</t>
+  </si>
+  <si>
+    <t>718497002 |Inherent location|</t>
+  </si>
+  <si>
+    <t>Observation.method</t>
+  </si>
+  <si>
+    <t>Méthode utilisée pour l'observation</t>
+  </si>
+  <si>
+    <t>Indicates the mechanism used to perform the observation.</t>
+  </si>
+  <si>
+    <t>Only used if not implicit in code for Observation.code.</t>
+  </si>
+  <si>
+    <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
+  </si>
+  <si>
     <t>example</t>
-  </si>
-  <si>
-    <t>Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
-  </si>
-  <si>
-    <t>&lt; 123037004 |Body structure|</t>
-  </si>
-  <si>
-    <t>OBX-20</t>
-  </si>
-  <si>
-    <t>targetSiteCode</t>
-  </si>
-  <si>
-    <t>718497002 |Inherent location|</t>
-  </si>
-  <si>
-    <t>Observation.method</t>
-  </si>
-  <si>
-    <t>Méthode utilisée pour l'observation</t>
-  </si>
-  <si>
-    <t>Indicates the mechanism used to perform the observation.</t>
-  </si>
-  <si>
-    <t>Only used if not implicit in code for Observation.code.</t>
-  </si>
-  <si>
-    <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
     <t>Methods for simple observations.</t>
@@ -1878,7 +1875,7 @@
 </t>
   </si>
   <si>
-    <t>Vital Sign Value recorded with UCUM</t>
+    <t>Valeur quantitative du signe vital</t>
   </si>
   <si>
     <t>Vital Sign Value recorded with UCUM.</t>
@@ -1887,10 +1884,7 @@
     <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/observation.html#notes) below.</t>
   </si>
   <si>
-    <t>Common UCUM units for recording Vital Signs.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/ucum-vitals-common|4.0.1</t>
+    <t>http://terminology.hl7.org/ValueSet/ucum-units</t>
   </si>
   <si>
     <t xml:space="preserve">vs-3
@@ -1898,137 +1892,6 @@
   </si>
   <si>
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].id</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].extension</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">decimal
-</t>
-  </si>
-  <si>
-    <t>Numerical value (with implicit precision)</t>
-  </si>
-  <si>
-    <t>The value of the measured amount. The value includes an implicit precision in the presentation of the value.</t>
-  </si>
-  <si>
-    <t>The implicit precision in the value should always be honored. Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
-  </si>
-  <si>
-    <t>Precision is handled implicitly in almost all cases of measurement.</t>
-  </si>
-  <si>
-    <t>Quantity.value</t>
-  </si>
-  <si>
-    <t>SN.2  / CQ - N/A</t>
-  </si>
-  <si>
-    <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].comparator</t>
-  </si>
-  <si>
-    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
-  </si>
-  <si>
-    <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
-  </si>
-  <si>
-    <t>Need a framework for handling measures where the value is &lt;5ug/L or &gt;400mg/L due to the limitations of measuring methodology.</t>
-  </si>
-  <si>
-    <t>If there is no comparator, then there is no modification of the value</t>
-  </si>
-  <si>
-    <t>How the Quantity should be understood and represented.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
-  </si>
-  <si>
-    <t>Quantity.comparator</t>
-  </si>
-  <si>
-    <t>SN.1  / CQ.1</t>
-  </si>
-  <si>
-    <t>IVL properties</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].unit</t>
-  </si>
-  <si>
-    <t>Unit representation</t>
-  </si>
-  <si>
-    <t>A human-readable form of the unit.</t>
-  </si>
-  <si>
-    <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
-  </si>
-  <si>
-    <t>Quantity.unit</t>
-  </si>
-  <si>
-    <t>(see OBX.6 etc.) / CQ.2</t>
-  </si>
-  <si>
-    <t>PQ.unit</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].system</t>
-  </si>
-  <si>
-    <t>Valeur quantitative du signe vital</t>
-  </si>
-  <si>
-    <t>The identification of the system that provides the coded form of the unit.</t>
-  </si>
-  <si>
-    <t>Need to know the system that defines the coded form of the unit.</t>
-  </si>
-  <si>
-    <t>http://unitsofmeasure.org</t>
-  </si>
-  <si>
-    <t>Quantity.system</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qty-3
-</t>
-  </si>
-  <si>
-    <t>CO.codeSystem, PQ.translation.codeSystem</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].code</t>
-  </si>
-  <si>
-    <t>Coded form of the unit</t>
-  </si>
-  <si>
-    <t>A computer processable form of the unit in some unit representation system.</t>
-  </si>
-  <si>
-    <t>The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
-  </si>
-  <si>
-    <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
-  </si>
-  <si>
-    <t>Quantity.code</t>
-  </si>
-  <si>
-    <t>PQ.code, MO.currency, PQ.translation.code</t>
   </si>
   <si>
     <t>Observation.component.dataAbsentReason</t>
@@ -2383,7 +2246,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP96"/>
+  <dimension ref="A1:AP89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="57.22265625" customWidth="true" bestFit="true"/>
@@ -10109,7 +9972,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
         <v>471</v>
       </c>
@@ -10128,7 +9991,7 @@
         <v>93</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>82</v>
@@ -10172,13 +10035,11 @@
         <v>82</v>
       </c>
       <c r="X65" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="Y65" s="2"/>
+      <c r="Z65" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>82</v>
@@ -10214,27 +10075,27 @@
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="AM65" t="s" s="2">
+      <c r="AO65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP65" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>481</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10260,16 +10121,16 @@
         <v>191</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10294,14 +10155,14 @@
         <v>82</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="Y66" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="Z66" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="Z66" t="s" s="2">
-        <v>488</v>
-      </c>
       <c r="AA66" t="s" s="2">
         <v>82</v>
       </c>
@@ -10318,7 +10179,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10339,10 +10200,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10353,10 +10214,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10379,16 +10240,16 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10438,7 +10299,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10456,27 +10317,27 @@
         <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AM67" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="AM67" t="s" s="2">
+      <c r="AN67" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="AN67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP67" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>499</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10499,16 +10360,16 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10558,7 +10419,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10576,27 +10437,27 @@
         <v>82</v>
       </c>
       <c r="AL68" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AM68" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="AM68" t="s" s="2">
+      <c r="AN68" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="AN68" t="s" s="2">
+      <c r="AO68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP68" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>508</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10619,19 +10480,19 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="N69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10680,7 +10541,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10692,19 +10553,19 @@
         <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM69" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="AK69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM69" t="s" s="2">
+      <c r="AN69" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10715,10 +10576,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10833,10 +10694,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10953,14 +10814,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10982,10 +10843,10 @@
         <v>139</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>142</v>
@@ -11040,7 +10901,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11075,10 +10936,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11101,13 +10962,13 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11158,7 +11019,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11167,7 +11028,7 @@
         <v>93</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>105</v>
@@ -11179,10 +11040,10 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AN73" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11193,10 +11054,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11219,13 +11080,13 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11276,7 +11137,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11285,7 +11146,7 @@
         <v>93</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>105</v>
@@ -11297,10 +11158,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11311,10 +11172,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11340,16 +11201,16 @@
         <v>191</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="N75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11377,11 +11238,11 @@
         <v>117</v>
       </c>
       <c r="Y75" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="Z75" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="Z75" t="s" s="2">
-        <v>542</v>
-      </c>
       <c r="AA75" t="s" s="2">
         <v>82</v>
       </c>
@@ -11398,7 +11259,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11416,10 +11277,10 @@
         <v>82</v>
       </c>
       <c r="AL75" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AM75" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>461</v>
@@ -11433,10 +11294,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11462,16 +11323,16 @@
         <v>191</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="N76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11496,14 +11357,14 @@
         <v>82</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="Y76" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="Z76" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="Z76" t="s" s="2">
-        <v>551</v>
-      </c>
       <c r="AA76" t="s" s="2">
         <v>82</v>
       </c>
@@ -11520,7 +11381,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11538,10 +11399,10 @@
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AM76" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>461</v>
@@ -11555,10 +11416,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11581,17 +11442,17 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11640,7 +11501,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11664,7 +11525,7 @@
         <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11675,10 +11536,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11704,10 +11565,10 @@
         <v>206</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11758,7 +11619,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11779,10 +11640,10 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11793,10 +11654,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11819,16 +11680,16 @@
         <v>94</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11878,7 +11739,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11899,10 +11760,10 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AN79" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -11913,10 +11774,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11939,16 +11800,16 @@
         <v>94</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="L80" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="M80" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11998,7 +11859,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12019,10 +11880,10 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -12033,10 +11894,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12059,19 +11920,19 @@
         <v>94</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="N81" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="M81" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="N81" t="s" s="2">
+      <c r="O81" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>578</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12120,7 +11981,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12132,19 +11993,19 @@
         <v>82</v>
       </c>
       <c r="AJ81" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM81" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="AK81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM81" t="s" s="2">
+      <c r="AN81" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12155,10 +12016,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12273,10 +12134,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12393,14 +12254,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12422,10 +12283,10 @@
         <v>139</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>142</v>
@@ -12480,7 +12341,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12515,10 +12376,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12544,16 +12405,16 @@
         <v>191</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="N85" t="s" s="2">
+      <c r="O85" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12581,11 +12442,11 @@
         <v>418</v>
       </c>
       <c r="Y85" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="Z85" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="Z85" t="s" s="2">
-        <v>591</v>
-      </c>
       <c r="AA85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12602,7 +12463,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>93</v>
@@ -12620,7 +12481,7 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>294</v>
@@ -12637,10 +12498,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12663,16 +12524,16 @@
         <v>94</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="M86" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="O86" t="s" s="2">
         <v>437</v>
@@ -12700,40 +12561,38 @@
         <v>82</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="Y86" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="Y86" s="2"/>
+      <c r="Z86" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI86" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="AG86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH86" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI86" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>105</v>
@@ -12742,7 +12601,7 @@
         <v>82</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>440</v>
@@ -12757,12 +12616,12 @@
         <v>442</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12776,7 +12635,7 @@
         <v>93</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>82</v>
@@ -12785,16 +12644,20 @@
         <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>207</v>
+        <v>601</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+        <v>602</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>447</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
       </c>
@@ -12818,13 +12681,13 @@
         <v>82</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>82</v>
+        <v>418</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>82</v>
+        <v>448</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>82</v>
@@ -12842,7 +12705,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>209</v>
+        <v>600</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12851,10 +12714,10 @@
         <v>93</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>82</v>
+        <v>604</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -12863,10 +12726,10 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>210</v>
+        <v>451</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -12877,14 +12740,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>138</v>
+        <v>453</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12903,18 +12766,20 @@
         <v>82</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>139</v>
+        <v>191</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>140</v>
+        <v>606</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>213</v>
+        <v>455</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O88" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -12938,31 +12803,31 @@
         <v>82</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>82</v>
+        <v>418</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>82</v>
+        <v>607</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>82</v>
+        <v>608</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>214</v>
+        <v>82</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>215</v>
+        <v>82</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>216</v>
+        <v>605</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12974,33 +12839,33 @@
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>82</v>
+        <v>459</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>82</v>
+        <v>460</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>210</v>
+        <v>461</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>82</v>
+        <v>462</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13011,7 +12876,7 @@
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>82</v>
@@ -13020,22 +12885,22 @@
         <v>82</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>605</v>
+        <v>83</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>608</v>
+        <v>512</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>609</v>
+        <v>513</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -13084,13 +12949,13 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>82</v>
@@ -13105,870 +12970,20 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>611</v>
+        <v>515</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>612</v>
+        <v>516</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="90" hidden="true">
-      <c r="A90" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="C90" s="2"/>
-      <c r="D90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E90" s="2"/>
-      <c r="F90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G90" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I90" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="J90" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K90" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="N90" s="2"/>
-      <c r="O90" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="P90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q90" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="R90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ90" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP90" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="91" hidden="true">
-      <c r="A91" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="C91" s="2"/>
-      <c r="D91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E91" s="2"/>
-      <c r="F91" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G91" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J91" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K91" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="L91" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="P91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q91" s="2"/>
-      <c r="R91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="AG91" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ91" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP91" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="92" hidden="true">
-      <c r="A92" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="C92" s="2"/>
-      <c r="D92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E92" s="2"/>
-      <c r="F92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G92" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J92" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K92" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L92" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="N92" s="2"/>
-      <c r="O92" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="P92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q92" s="2"/>
-      <c r="R92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S92" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="T92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="AG92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH92" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI92" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="AJ92" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP92" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="93" hidden="true">
-      <c r="A93" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="C93" s="2"/>
-      <c r="D93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E93" s="2"/>
-      <c r="F93" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G93" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J93" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K93" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="L93" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="P93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q93" s="2"/>
-      <c r="R93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="AG93" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH93" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ93" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP93" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="C94" s="2"/>
-      <c r="D94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E94" s="2"/>
-      <c r="F94" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G94" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H94" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K94" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L94" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="P94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q94" s="2"/>
-      <c r="R94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="AG94" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH94" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI94" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="AJ94" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP94" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="95" hidden="true">
-      <c r="A95" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="C95" s="2"/>
-      <c r="D95" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="E95" s="2"/>
-      <c r="F95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K95" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L95" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="P95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q95" s="2"/>
-      <c r="R95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X95" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="Z95" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="AG95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ95" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP95" t="s" s="2">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="96" hidden="true">
-      <c r="A96" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="C96" s="2"/>
-      <c r="D96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E96" s="2"/>
-      <c r="F96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="P96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q96" s="2"/>
-      <c r="R96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP96" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP96">
+  <autoFilter ref="A1:AP89">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13978,7 +12993,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI95">
+  <conditionalFormatting sqref="A2:AI88">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T15:31:02+00:00</t>
+    <t>2026-06-16T14:27:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:27:29+00:00</t>
+    <t>2026-06-18T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-vital-signs-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:40:49+00:00</t>
+    <t>2026-06-22T09:35:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
